--- a/output/pdf_financials_xlsx/SASK.xlsx
+++ b/output/pdf_financials_xlsx/SASK.xlsx
@@ -2476,19 +2476,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.000437</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.567744</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>9.428217</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>3.991403</v>
+        <v>18.525576</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1.563594</v>
+        <v>16.734551</v>
       </c>
     </row>
     <row r="93">
@@ -3080,7 +3080,7 @@
         <v>-18.189103</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-30.444726</v>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
@@ -4580,7 +4580,11 @@
           <t>Share-based payment reserve 14</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -5906,7 +5910,11 @@
           <t>Share-based payment reserve 15 14,534,173</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -6971,7 +6979,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -7389,7 +7401,11 @@
           <t>Share‐based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>0.000437</v>
       </c>
@@ -7598,7 +7614,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="n">
         <v>0.000437</v>
       </c>
@@ -8321,7 +8341,11 @@
           <t>Exploration and evaluation expenditures $</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SASK.xlsx
+++ b/output/pdf_financials_xlsx/SASK.xlsx
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1.156738</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.862379</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.190705</v>
       </c>
     </row>
     <row r="13">
@@ -1027,13 +1027,13 @@
         <v>-1.030243</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-13.975627</v>
+        <v>-15.132365</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-13.269174</v>
+        <v>-14.131553</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.485670000000001</v>
+        <v>-8.676375</v>
       </c>
     </row>
     <row r="28">
@@ -1071,13 +1071,13 @@
         <v>-1.030243</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-13.945669</v>
+        <v>-15.102407</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-13.042043</v>
+        <v>-13.904422</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.485670000000001</v>
+        <v>-8.676375</v>
       </c>
     </row>
     <row r="30">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.018339</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>6.976683</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>33.322911</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>8.110541</v>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.018339</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>6.976683</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.683333</v>
+        <v>34.006244</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>8.262504</v>
@@ -1491,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>40.719417</v>
+        <v>33.742734</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>38.414914</v>
+        <v>5.092003</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1.00493</v>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">

--- a/output/pdf_financials_xlsx/SASK.xlsx
+++ b/output/pdf_financials_xlsx/SASK.xlsx
@@ -565,13 +565,13 @@
         <v>0.196643</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.5811460000000001</v>
+        <v>0.920646</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.126166</v>
+        <v>2.294953</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.566663</v>
+        <v>1.808717</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +791,7 @@
         <v>3.475001</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.101825</v>
+        <v>3.218448</v>
       </c>
     </row>
     <row r="18">
@@ -1131,7 +1131,7 @@
         <v>-26.18852537467668</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-1.199964174897209</v>
+        <v>-37.9280363247687</v>
       </c>
     </row>
     <row r="32">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005222</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.030034</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.77466</v>
@@ -8675,7 +8675,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -9427,7 +9431,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>-0.005222</v>
       </c>
@@ -9759,7 +9767,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -10814,7 +10826,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E171" s="5" t="n">
         <v>-0.005222</v>
       </c>
@@ -10892,7 +10908,11 @@
           <t>Proceeds from share issuance (Note 7)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E173" s="5" t="n">
         <v>0.025</v>
       </c>
@@ -11179,7 +11199,11 @@
           <t>Proceeds from share issuance (Note 6b)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E180" s="5" t="n">
         <v>0.025</v>
       </c>
@@ -11611,7 +11635,11 @@
           <t>Director fees 15</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -12306,7 +12334,11 @@
           <t>Deferred income tax recovery (expense) 19</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -12946,7 +12978,11 @@
           <t>Management and director fees 16</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
